--- a/src/test/resources/testdata/TestOutput.xlsx
+++ b/src/test/resources/testdata/TestOutput.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="46">
   <si>
     <t>S.No</t>
   </si>
@@ -66,6 +66,99 @@
   </si>
   <si>
     <t>Dining Room</t>
+  </si>
+  <si>
+    <t>TC_08 Discount High To Low</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>D'Dass Red Wooden Shelf Style Temple For Pooja In Home and Office</t>
+  </si>
+  <si>
+    <t>72% OFF</t>
+  </si>
+  <si>
+    <t>BLUEWUD Maisy Standard Engineering Wood Wall Mount TV Entertainment Unit Set Top Box Stand/TV Cabinet Panel with Shelves for Books &amp; Decor Display Unit Standard Upto 42 Inches (Brown Maple &amp; White)</t>
+  </si>
+  <si>
+    <t>70% OFF</t>
+  </si>
+  <si>
+    <t>BLUEWUD Millie Engineering Wood Wall Mount TV Entertainment Unit Set Top Box Stand/TV Cabinet Panel with Shelves for Books &amp; Decor Display Unit Bed Living Room Upto 50 Inches (Brown Maple)</t>
+  </si>
+  <si>
+    <t>69% OFF</t>
+  </si>
+  <si>
+    <t>Phelix Engineered Wood Bookshelf in Wenge Finish</t>
+  </si>
+  <si>
+    <t>68% OFF</t>
+  </si>
+  <si>
+    <t>BLUEWUD Estoye Mini Engineering Wood Wall Mount TV Entertainment Unit Set Top Box Stand/TV Cabinet Panel with Shelves for Books &amp; Decor Display Unit, Ideal for 42Inches(Brown Maple)</t>
+  </si>
+  <si>
+    <t>65% OFF</t>
+  </si>
+  <si>
+    <t>BLUEWUD Aaron Engineered Wood Multipurpose Wall Decor Shelf (Wenge)</t>
+  </si>
+  <si>
+    <t>BLUEWUD Kyvid Large Engineering Wood Wall Mount TV Entertainment Unit Set Top Box Stand/TV Cabinet Panel with Shelves for Books &amp; Decor Display Unit Large Upto 50 Inches (Wenge)</t>
+  </si>
+  <si>
+    <t>63% OFF</t>
+  </si>
+  <si>
+    <t>Display Engineered Wood Bookshelf in Walnut Finish</t>
+  </si>
+  <si>
+    <t>62% OFF</t>
+  </si>
+  <si>
+    <t>Song Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>Essence Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>61% OFF</t>
+  </si>
+  <si>
+    <t>Henry Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>Darren Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>TC_08 - Discount High To Low</t>
+  </si>
+  <si>
+    <t>Larry Engineered Wood Bookshelf in Graphgite Grey &amp; Frosty White Finish</t>
+  </si>
+  <si>
+    <t>Amy Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>Drake Engineered Wood Bookshelf in Columbian Walnut Finish</t>
+  </si>
+  <si>
+    <t>BLUEWUD Astrella Engineered Wood Wall Mount Decorative Shelf (Wenge)</t>
+  </si>
+  <si>
+    <t>BLUEWUD Primax Solo Large Engineering Wood Wall Mount TV Entertainment Unit Set Top Box Stand/TV Cabinet Panel with Shelves for Books &amp; Decor Display Unit, Ideal for 55Inches (Wenge &amp; White)</t>
+  </si>
+  <si>
+    <t>59% OFF</t>
+  </si>
+  <si>
+    <t>Javis Engineered Wood Bookshelf in Brown Maple Finish</t>
+  </si>
+  <si>
+    <t>BLUEWUD Javies Engineered Wood Multipurpose Wall Decor Shelf (Wenge)</t>
   </si>
 </sst>
 </file>
@@ -438,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -516,6 +609,659 @@
       </c>
       <c r="C7" t="s" s="0">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n" s="0">
+        <v>48.0</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n" s="0">
+        <v>49.0</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4018DD7B-01A5-4810-8DB3-FB76076E4E02}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="19.0"/>
@@ -611,6 +1357,46 @@
         <v>14</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
